--- a/Assets/08.Excel/GameData.xlsx
+++ b/Assets/08.Excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\My idle game\my-idle-game\Assets\08.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7421EAF-FCDE-4824-9B74-DB5E31DE43D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37DA9F5-41E5-435E-BEC8-77B5B2CD68DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -214,43 +214,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet1_0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet1_1]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet1_2]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet1_3]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet2_0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet2_1]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet2_2]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet2_3]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet3_0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet3_1]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet3_2]</t>
-  </si>
-  <si>
-    <t>Assets/00.Externals/Myaddressable/item/itemSheet0.png[itemSheet3_3]</t>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet1.png[itemSheet1_0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet1.png[itemSheet1_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet1.png[itemSheet1_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet1.png[itemSheet1_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet2.png[itemSheet2_0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet2.png[itemSheet2_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet2.png[itemSheet2_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet2.png[itemSheet2_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet3.png[itemSheet3_0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet3.png[itemSheet3_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet3.png[itemSheet3_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/item/itemSheet3.png[itemSheet3_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -788,15 +797,6 @@
     <xf numFmtId="178" fontId="4" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -811,6 +811,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1637,155 +1646,155 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="57" t="str">
+    <row r="14" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="54" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H3,"000")</f>
         <v>101003001</v>
       </c>
-      <c r="B14" s="58" t="str">
+      <c r="B14" s="55" t="str">
         <f>규칙!B8</f>
         <v>Helmet</v>
       </c>
-      <c r="C14" s="58">
+      <c r="C14" s="55">
         <v>5000</v>
       </c>
-      <c r="D14" s="58">
-        <v>0</v>
-      </c>
-      <c r="E14" s="58">
-        <v>0</v>
-      </c>
-      <c r="F14" s="58">
-        <v>0</v>
-      </c>
-      <c r="G14" s="58">
-        <v>0</v>
-      </c>
-      <c r="H14" s="59">
+      <c r="D14" s="55">
+        <v>0</v>
+      </c>
+      <c r="E14" s="55">
+        <v>0</v>
+      </c>
+      <c r="F14" s="55">
+        <v>0</v>
+      </c>
+      <c r="G14" s="55">
+        <v>0</v>
+      </c>
+      <c r="H14" s="56">
         <v>10000</v>
       </c>
-      <c r="I14" s="58">
+      <c r="I14" s="55">
         <v>3</v>
       </c>
-      <c r="J14" s="58" t="str">
+      <c r="J14" s="55" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K14" s="60" t="s">
+      <c r="K14" s="57" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="57" t="str">
+    <row r="15" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="54" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H4,"000")</f>
         <v>101003002</v>
       </c>
-      <c r="B15" s="58" t="str">
+      <c r="B15" s="55" t="str">
         <f>규칙!B9</f>
         <v>Weapon</v>
       </c>
-      <c r="C15" s="58">
-        <v>0</v>
-      </c>
-      <c r="D15" s="58">
+      <c r="C15" s="55">
+        <v>0</v>
+      </c>
+      <c r="D15" s="55">
         <v>80</v>
       </c>
-      <c r="E15" s="58">
-        <v>0</v>
-      </c>
-      <c r="F15" s="58">
-        <v>0</v>
-      </c>
-      <c r="G15" s="58">
-        <v>0</v>
-      </c>
-      <c r="H15" s="59">
+      <c r="E15" s="55">
+        <v>0</v>
+      </c>
+      <c r="F15" s="55">
+        <v>0</v>
+      </c>
+      <c r="G15" s="55">
+        <v>0</v>
+      </c>
+      <c r="H15" s="56">
         <v>15000</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="55">
         <v>3</v>
       </c>
-      <c r="J15" s="58" t="str">
+      <c r="J15" s="55" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K15" s="60" t="s">
+      <c r="K15" s="57" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="57" t="str">
+    <row r="16" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="54" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H5,"000")</f>
         <v>101003003</v>
       </c>
-      <c r="B16" s="58" t="str">
+      <c r="B16" s="55" t="str">
         <f>규칙!B10</f>
         <v>Shield</v>
       </c>
-      <c r="C16" s="58">
-        <v>0</v>
-      </c>
-      <c r="D16" s="58">
-        <v>0</v>
-      </c>
-      <c r="E16" s="58">
+      <c r="C16" s="55">
+        <v>0</v>
+      </c>
+      <c r="D16" s="55">
+        <v>0</v>
+      </c>
+      <c r="E16" s="55">
         <v>35</v>
       </c>
-      <c r="F16" s="58">
-        <v>0</v>
-      </c>
-      <c r="G16" s="58">
-        <v>0</v>
-      </c>
-      <c r="H16" s="59">
+      <c r="F16" s="55">
+        <v>0</v>
+      </c>
+      <c r="G16" s="55">
+        <v>0</v>
+      </c>
+      <c r="H16" s="56">
         <v>12000</v>
       </c>
-      <c r="I16" s="58">
+      <c r="I16" s="55">
         <v>3</v>
       </c>
-      <c r="J16" s="58" t="str">
+      <c r="J16" s="55" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="57" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="57" t="str">
+    <row r="17" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="54" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H6,"000")</f>
         <v>101003004</v>
       </c>
-      <c r="B17" s="58" t="str">
+      <c r="B17" s="55" t="str">
         <f>규칙!B11</f>
         <v>Ring</v>
       </c>
-      <c r="C17" s="58">
-        <v>0</v>
-      </c>
-      <c r="D17" s="58">
-        <v>0</v>
-      </c>
-      <c r="E17" s="58">
-        <v>0</v>
-      </c>
-      <c r="F17" s="58">
+      <c r="C17" s="55">
+        <v>0</v>
+      </c>
+      <c r="D17" s="55">
+        <v>0</v>
+      </c>
+      <c r="E17" s="55">
+        <v>0</v>
+      </c>
+      <c r="F17" s="55">
         <v>55</v>
       </c>
-      <c r="G17" s="58">
-        <v>0</v>
-      </c>
-      <c r="H17" s="59">
+      <c r="G17" s="55">
+        <v>0</v>
+      </c>
+      <c r="H17" s="56">
         <v>18000</v>
       </c>
-      <c r="I17" s="58">
+      <c r="I17" s="55">
         <v>3</v>
       </c>
-      <c r="J17" s="58" t="str">
+      <c r="J17" s="55" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K17" s="60" t="s">
+      <c r="K17" s="57" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1819,19 +1828,19 @@
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="E2" s="54" t="s">
+      <c r="C2" s="60"/>
+      <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="H2" s="54" t="s">
+      <c r="F2" s="60"/>
+      <c r="H2" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="55"/>
-      <c r="K2" s="56" t="s">
+      <c r="I2" s="60"/>
+      <c r="K2" s="61" t="s">
         <v>44</v>
       </c>
       <c r="L2" s="14" t="s">
@@ -1862,7 +1871,7 @@
       <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="56"/>
+      <c r="K3" s="61"/>
       <c r="L3" s="12" t="s">
         <v>24</v>
       </c>

--- a/Assets/08.Excel/GameData.xlsx
+++ b/Assets/08.Excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\My idle game\my-idle-game\Assets\08.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37DA9F5-41E5-435E-BEC8-77B5B2CD68DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABA9551-0E3C-450A-A26F-F6E964E18C12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
   </bookViews>
@@ -1504,13 +1504,13 @@
         <v>Helmet</v>
       </c>
       <c r="C10" s="31">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D10" s="31">
         <v>0</v>
       </c>
       <c r="E10" s="31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F10" s="31">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G11" s="35">
         <v>0</v>
@@ -1580,13 +1580,13 @@
         <v>Shield</v>
       </c>
       <c r="C12" s="35">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="D12" s="35">
         <v>0</v>
       </c>
       <c r="E12" s="35">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F12" s="35">
         <v>0</v>
@@ -1621,13 +1621,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E13" s="35">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F13" s="35">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G13" s="35">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>Helmet</v>
       </c>
       <c r="C14" s="55">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="D14" s="55">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="55">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E15" s="55">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="55">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F16" s="55">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="55">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="G17" s="55">
         <v>0</v>

--- a/Assets/08.Excel/GameData.xlsx
+++ b/Assets/08.Excel/GameData.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\My idle game\my-idle-game\Assets\08.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABA9551-0E3C-450A-A26F-F6E964E18C12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD51D7F-8F1C-46F7-823C-E6154FCE29D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" activeTab="2" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemSheet" sheetId="1" r:id="rId1"/>
-    <sheet name="규칙" sheetId="2" r:id="rId2"/>
+    <sheet name="DailyReward" sheetId="3" r:id="rId2"/>
+    <sheet name="규칙" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -260,6 +261,147 @@
   <si>
     <t>Assets/00.Externals/Myaddressable/item/itemSheet3.png[itemSheet3_3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출석 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세번째규칙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ex.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두번째규칙(일별)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1일 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31일 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>랜덤 아이템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/00.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/01.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/02.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/03.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/04.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/05.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/06.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/07.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/08.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/09.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/10.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/11.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/12.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/13.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/14.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/15.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/16.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/17.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/18.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/19.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/20.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/21.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/22.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/23.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/24.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/25.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/26.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/27.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/28.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/29.Externals/Myaddressable/G_coin.png[G_coin]</t>
+  </si>
+  <si>
+    <t>Assets/30.Externals/Myaddressable/G_coin.png[G_coin]</t>
   </si>
 </sst>
 </file>
@@ -271,7 +413,7 @@
     <numFmt numFmtId="177" formatCode="00000000"/>
     <numFmt numFmtId="178" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,8 +485,40 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,8 +561,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9999FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -480,17 +666,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -634,7 +809,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -671,147 +846,177 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="7" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -819,6 +1024,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -829,12 +1043,12 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9999FF"/>
       <color rgb="FFF5F51B"/>
-      <color rgb="FFFFFFFF"/>
       <color rgb="FFFFF8A3"/>
       <color rgb="FF9966FF"/>
       <color rgb="FF6699FF"/>
-      <color rgb="FF9999FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1148,653 +1362,653 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.69921875" style="27" customWidth="1"/>
-    <col min="2" max="7" width="16.69921875" style="28" customWidth="1"/>
-    <col min="8" max="8" width="16.69921875" style="48" customWidth="1"/>
-    <col min="9" max="10" width="16.69921875" style="28" customWidth="1"/>
+    <col min="1" max="1" width="16.69921875" style="25" customWidth="1"/>
+    <col min="2" max="7" width="16.69921875" style="26" customWidth="1"/>
+    <col min="8" max="8" width="16.69921875" style="46" customWidth="1"/>
+    <col min="9" max="10" width="16.69921875" style="26" customWidth="1"/>
     <col min="11" max="11" width="61.296875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28" t="s">
+    <row r="1" spans="1:11" s="27" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="48" t="s">
+      <c r="H1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="26" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="41" t="str">
+    <row r="2" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="39" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$3,"000")&amp;TEXT(규칙!H3,"000")</f>
         <v>101000001</v>
       </c>
-      <c r="B2" s="42" t="str">
+      <c r="B2" s="40" t="str">
         <f>규칙!B8</f>
         <v>Helmet</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C2" s="40">
         <v>500</v>
       </c>
-      <c r="D2" s="42">
-        <v>0</v>
-      </c>
-      <c r="E2" s="42">
-        <v>0</v>
-      </c>
-      <c r="F2" s="42">
-        <v>0</v>
-      </c>
-      <c r="G2" s="42">
-        <v>0</v>
-      </c>
-      <c r="H2" s="49">
+      <c r="D2" s="40">
+        <v>0</v>
+      </c>
+      <c r="E2" s="40">
+        <v>0</v>
+      </c>
+      <c r="F2" s="40">
+        <v>0</v>
+      </c>
+      <c r="G2" s="40">
+        <v>0</v>
+      </c>
+      <c r="H2" s="47">
         <v>500</v>
       </c>
-      <c r="I2" s="42">
-        <v>0</v>
-      </c>
-      <c r="J2" s="42" t="str">
+      <c r="I2" s="40">
+        <v>0</v>
+      </c>
+      <c r="J2" s="40" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K2" s="43" t="s">
+      <c r="K2" s="41" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="47" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="45" t="str">
+    <row r="3" spans="1:11" s="45" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="43" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$3,"000")&amp;TEXT(규칙!H4,"000")</f>
         <v>101000002</v>
       </c>
-      <c r="B3" s="46" t="str">
+      <c r="B3" s="44" t="str">
         <f>규칙!B9</f>
         <v>Weapon</v>
       </c>
-      <c r="C3" s="46">
-        <v>0</v>
-      </c>
-      <c r="D3" s="46">
+      <c r="C3" s="44">
+        <v>0</v>
+      </c>
+      <c r="D3" s="44">
         <v>5</v>
       </c>
-      <c r="E3" s="46">
-        <v>0</v>
-      </c>
-      <c r="F3" s="46">
-        <v>0</v>
-      </c>
-      <c r="G3" s="46">
-        <v>0</v>
-      </c>
-      <c r="H3" s="50">
+      <c r="E3" s="44">
+        <v>0</v>
+      </c>
+      <c r="F3" s="44">
+        <v>0</v>
+      </c>
+      <c r="G3" s="44">
+        <v>0</v>
+      </c>
+      <c r="H3" s="48">
         <v>1000</v>
       </c>
-      <c r="I3" s="46">
-        <v>0</v>
-      </c>
-      <c r="J3" s="46" t="str">
+      <c r="I3" s="44">
+        <v>0</v>
+      </c>
+      <c r="J3" s="44" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K3" s="43" t="s">
+      <c r="K3" s="41" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="47" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="45" t="str">
+    <row r="4" spans="1:11" s="45" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="43" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$3,"000")&amp;TEXT(규칙!H5,"000")</f>
         <v>101000003</v>
       </c>
-      <c r="B4" s="46" t="str">
+      <c r="B4" s="44" t="str">
         <f>규칙!B10</f>
         <v>Shield</v>
       </c>
-      <c r="C4" s="46">
-        <v>0</v>
-      </c>
-      <c r="D4" s="46">
-        <v>0</v>
-      </c>
-      <c r="E4" s="46">
+      <c r="C4" s="44">
+        <v>0</v>
+      </c>
+      <c r="D4" s="44">
+        <v>0</v>
+      </c>
+      <c r="E4" s="44">
         <v>2</v>
       </c>
-      <c r="F4" s="46">
-        <v>0</v>
-      </c>
-      <c r="G4" s="46">
-        <v>0</v>
-      </c>
-      <c r="H4" s="50">
+      <c r="F4" s="44">
+        <v>0</v>
+      </c>
+      <c r="G4" s="44">
+        <v>0</v>
+      </c>
+      <c r="H4" s="48">
         <v>800</v>
       </c>
-      <c r="I4" s="46">
-        <v>0</v>
-      </c>
-      <c r="J4" s="46" t="str">
+      <c r="I4" s="44">
+        <v>0</v>
+      </c>
+      <c r="J4" s="44" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K4" s="43" t="s">
+      <c r="K4" s="41" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="47" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="45" t="str">
+    <row r="5" spans="1:11" s="45" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="43" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$3,"000")&amp;TEXT(규칙!H6,"000")</f>
         <v>101000004</v>
       </c>
-      <c r="B5" s="46" t="str">
+      <c r="B5" s="44" t="str">
         <f>규칙!B11</f>
         <v>Ring</v>
       </c>
-      <c r="C5" s="46">
-        <v>0</v>
-      </c>
-      <c r="D5" s="46">
-        <v>0</v>
-      </c>
-      <c r="E5" s="46">
-        <v>0</v>
-      </c>
-      <c r="F5" s="46">
+      <c r="C5" s="44">
+        <v>0</v>
+      </c>
+      <c r="D5" s="44">
+        <v>0</v>
+      </c>
+      <c r="E5" s="44">
+        <v>0</v>
+      </c>
+      <c r="F5" s="44">
         <v>5</v>
       </c>
-      <c r="G5" s="46">
-        <v>0</v>
-      </c>
-      <c r="H5" s="50">
+      <c r="G5" s="44">
+        <v>0</v>
+      </c>
+      <c r="H5" s="48">
         <v>1200</v>
       </c>
-      <c r="I5" s="46">
-        <v>0</v>
-      </c>
-      <c r="J5" s="46" t="str">
+      <c r="I5" s="44">
+        <v>0</v>
+      </c>
+      <c r="J5" s="44" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="41" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="37" t="str">
+    <row r="6" spans="1:11" s="38" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="35" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$4,"000")&amp;TEXT(규칙!H3,"000")</f>
         <v>101001001</v>
       </c>
-      <c r="B6" s="38" t="str">
+      <c r="B6" s="36" t="str">
         <f>규칙!B8</f>
         <v>Helmet</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="36">
         <v>3500</v>
       </c>
-      <c r="D6" s="38">
-        <v>0</v>
-      </c>
-      <c r="E6" s="38">
-        <v>0</v>
-      </c>
-      <c r="F6" s="38">
-        <v>0</v>
-      </c>
-      <c r="G6" s="38">
-        <v>0</v>
-      </c>
-      <c r="H6" s="51">
+      <c r="D6" s="36">
+        <v>0</v>
+      </c>
+      <c r="E6" s="36">
+        <v>0</v>
+      </c>
+      <c r="F6" s="36">
+        <v>0</v>
+      </c>
+      <c r="G6" s="36">
+        <v>0</v>
+      </c>
+      <c r="H6" s="49">
         <v>3500</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="36">
         <v>1</v>
       </c>
-      <c r="J6" s="38" t="str">
+      <c r="J6" s="36" t="str">
         <f>규칙!$B$13</f>
         <v>None</v>
       </c>
-      <c r="K6" s="39" t="s">
+      <c r="K6" s="37" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="37" t="str">
+    <row r="7" spans="1:11" s="38" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="35" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$4,"000")&amp;TEXT(규칙!H4,"000")</f>
         <v>101001002</v>
       </c>
-      <c r="B7" s="38" t="str">
+      <c r="B7" s="36" t="str">
         <f>규칙!B9</f>
         <v>Weapon</v>
       </c>
-      <c r="C7" s="38">
-        <v>0</v>
-      </c>
-      <c r="D7" s="38">
+      <c r="C7" s="36">
+        <v>0</v>
+      </c>
+      <c r="D7" s="36">
         <v>30</v>
       </c>
-      <c r="E7" s="38">
-        <v>0</v>
-      </c>
-      <c r="F7" s="38">
-        <v>0</v>
-      </c>
-      <c r="G7" s="38">
-        <v>0</v>
-      </c>
-      <c r="H7" s="51">
+      <c r="E7" s="36">
+        <v>0</v>
+      </c>
+      <c r="F7" s="36">
+        <v>0</v>
+      </c>
+      <c r="G7" s="36">
+        <v>0</v>
+      </c>
+      <c r="H7" s="49">
         <v>5000</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="36">
         <v>1</v>
       </c>
-      <c r="J7" s="38" t="str">
+      <c r="J7" s="36" t="str">
         <f>규칙!$B$13</f>
         <v>None</v>
       </c>
-      <c r="K7" s="39" t="s">
+      <c r="K7" s="37" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="37" t="str">
+    <row r="8" spans="1:11" s="38" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="35" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$4,"000")&amp;TEXT(규칙!H5,"000")</f>
         <v>101001003</v>
       </c>
-      <c r="B8" s="38" t="str">
+      <c r="B8" s="36" t="str">
         <f>규칙!B10</f>
         <v>Shield</v>
       </c>
-      <c r="C8" s="38">
-        <v>0</v>
-      </c>
-      <c r="D8" s="38">
-        <v>0</v>
-      </c>
-      <c r="E8" s="38">
+      <c r="C8" s="36">
+        <v>0</v>
+      </c>
+      <c r="D8" s="36">
+        <v>0</v>
+      </c>
+      <c r="E8" s="36">
         <v>12</v>
       </c>
-      <c r="F8" s="38">
-        <v>0</v>
-      </c>
-      <c r="G8" s="38">
-        <v>0</v>
-      </c>
-      <c r="H8" s="51">
+      <c r="F8" s="36">
+        <v>0</v>
+      </c>
+      <c r="G8" s="36">
+        <v>0</v>
+      </c>
+      <c r="H8" s="49">
         <v>4500</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="36">
         <v>1</v>
       </c>
-      <c r="J8" s="38" t="str">
+      <c r="J8" s="36" t="str">
         <f>규칙!$B$13</f>
         <v>None</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="37" t="str">
+    <row r="9" spans="1:11" s="38" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="35" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$4,"000")&amp;TEXT(규칙!H6,"000")</f>
         <v>101001004</v>
       </c>
-      <c r="B9" s="38" t="str">
+      <c r="B9" s="36" t="str">
         <f>규칙!B11</f>
         <v>Ring</v>
       </c>
-      <c r="C9" s="38">
-        <v>0</v>
-      </c>
-      <c r="D9" s="38">
-        <v>0</v>
-      </c>
-      <c r="E9" s="38">
-        <v>0</v>
-      </c>
-      <c r="F9" s="38">
+      <c r="C9" s="36">
+        <v>0</v>
+      </c>
+      <c r="D9" s="36">
+        <v>0</v>
+      </c>
+      <c r="E9" s="36">
+        <v>0</v>
+      </c>
+      <c r="F9" s="36">
         <v>36</v>
       </c>
-      <c r="G9" s="38">
-        <v>0</v>
-      </c>
-      <c r="H9" s="51">
+      <c r="G9" s="36">
+        <v>0</v>
+      </c>
+      <c r="H9" s="49">
         <v>6000</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="36">
         <v>1</v>
       </c>
-      <c r="J9" s="38" t="str">
+      <c r="J9" s="36" t="str">
         <f>규칙!$B$13</f>
         <v>None</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="K9" s="37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="33" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="30" t="str">
+    <row r="10" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="28" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$5,"000")&amp;TEXT(규칙!H3,"000")</f>
         <v>101002001</v>
       </c>
-      <c r="B10" s="31" t="str">
+      <c r="B10" s="29" t="str">
         <f>규칙!B8</f>
         <v>Helmet</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="29">
         <v>5000</v>
       </c>
-      <c r="D10" s="31">
-        <v>0</v>
-      </c>
-      <c r="E10" s="31">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31">
-        <v>0</v>
-      </c>
-      <c r="H10" s="52">
+      <c r="D10" s="29">
+        <v>0</v>
+      </c>
+      <c r="E10" s="29">
+        <v>0</v>
+      </c>
+      <c r="F10" s="29">
+        <v>0</v>
+      </c>
+      <c r="G10" s="29">
+        <v>0</v>
+      </c>
+      <c r="H10" s="50">
         <v>4400</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="29">
         <v>2</v>
       </c>
-      <c r="J10" s="31" t="str">
+      <c r="J10" s="29" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K10" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="34" t="str">
+    <row r="11" spans="1:11" s="34" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="32" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$5,"000")&amp;TEXT(규칙!H4,"000")</f>
         <v>101002002</v>
       </c>
-      <c r="B11" s="35" t="str">
+      <c r="B11" s="33" t="str">
         <f>규칙!B9</f>
         <v>Weapon</v>
       </c>
-      <c r="C11" s="35">
-        <v>0</v>
-      </c>
-      <c r="D11" s="35">
+      <c r="C11" s="33">
+        <v>0</v>
+      </c>
+      <c r="D11" s="33">
         <v>32</v>
       </c>
-      <c r="E11" s="35">
-        <v>0</v>
-      </c>
-      <c r="F11" s="35">
-        <v>0</v>
-      </c>
-      <c r="G11" s="35">
-        <v>0</v>
-      </c>
-      <c r="H11" s="53">
+      <c r="E11" s="33">
+        <v>0</v>
+      </c>
+      <c r="F11" s="33">
+        <v>0</v>
+      </c>
+      <c r="G11" s="33">
+        <v>0</v>
+      </c>
+      <c r="H11" s="51">
         <v>5500</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="33">
         <v>2</v>
       </c>
-      <c r="J11" s="35" t="str">
+      <c r="J11" s="33" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K11" s="32" t="s">
+      <c r="K11" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="34" t="str">
+    <row r="12" spans="1:11" s="34" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="32" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$5,"000")&amp;TEXT(규칙!H5,"000")</f>
         <v>101002003</v>
       </c>
-      <c r="B12" s="35" t="str">
+      <c r="B12" s="33" t="str">
         <f>규칙!B10</f>
         <v>Shield</v>
       </c>
-      <c r="C12" s="35">
-        <v>0</v>
-      </c>
-      <c r="D12" s="35">
-        <v>0</v>
-      </c>
-      <c r="E12" s="35">
+      <c r="C12" s="33">
+        <v>0</v>
+      </c>
+      <c r="D12" s="33">
+        <v>0</v>
+      </c>
+      <c r="E12" s="33">
         <v>20</v>
       </c>
-      <c r="F12" s="35">
-        <v>0</v>
-      </c>
-      <c r="G12" s="35">
-        <v>0</v>
-      </c>
-      <c r="H12" s="53">
+      <c r="F12" s="33">
+        <v>0</v>
+      </c>
+      <c r="G12" s="33">
+        <v>0</v>
+      </c>
+      <c r="H12" s="51">
         <v>4800</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="33">
         <v>2</v>
       </c>
-      <c r="J12" s="35" t="str">
+      <c r="J12" s="33" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K12" s="32" t="s">
+      <c r="K12" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="34" t="str">
+    <row r="13" spans="1:11" s="34" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="32" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$5,"000")&amp;TEXT(규칙!H6,"000")</f>
         <v>101002004</v>
       </c>
-      <c r="B13" s="35" t="str">
+      <c r="B13" s="33" t="str">
         <f>규칙!B11</f>
         <v>Ring</v>
       </c>
-      <c r="C13" s="35">
-        <v>0</v>
-      </c>
-      <c r="D13" s="35">
-        <v>0</v>
-      </c>
-      <c r="E13" s="35">
-        <v>0</v>
-      </c>
-      <c r="F13" s="35">
+      <c r="C13" s="33">
+        <v>0</v>
+      </c>
+      <c r="D13" s="33">
+        <v>0</v>
+      </c>
+      <c r="E13" s="33">
+        <v>0</v>
+      </c>
+      <c r="F13" s="33">
         <v>50</v>
       </c>
-      <c r="G13" s="35">
-        <v>0</v>
-      </c>
-      <c r="H13" s="53">
+      <c r="G13" s="33">
+        <v>0</v>
+      </c>
+      <c r="H13" s="51">
         <v>6500</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="33">
         <v>2</v>
       </c>
-      <c r="J13" s="35" t="str">
+      <c r="J13" s="33" t="str">
         <f>규칙!$B$14</f>
         <v>Gold</v>
       </c>
-      <c r="K13" s="32" t="s">
+      <c r="K13" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="54" t="str">
+    <row r="14" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="52" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H3,"000")</f>
         <v>101003001</v>
       </c>
-      <c r="B14" s="55" t="str">
+      <c r="B14" s="53" t="str">
         <f>규칙!B8</f>
         <v>Helmet</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="53">
         <v>8000</v>
       </c>
-      <c r="D14" s="55">
-        <v>0</v>
-      </c>
-      <c r="E14" s="55">
-        <v>0</v>
-      </c>
-      <c r="F14" s="55">
-        <v>0</v>
-      </c>
-      <c r="G14" s="55">
-        <v>0</v>
-      </c>
-      <c r="H14" s="56">
+      <c r="D14" s="53">
+        <v>0</v>
+      </c>
+      <c r="E14" s="53">
+        <v>0</v>
+      </c>
+      <c r="F14" s="53">
+        <v>0</v>
+      </c>
+      <c r="G14" s="53">
+        <v>0</v>
+      </c>
+      <c r="H14" s="54">
         <v>10000</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="53">
         <v>3</v>
       </c>
-      <c r="J14" s="55" t="str">
+      <c r="J14" s="53" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K14" s="57" t="s">
+      <c r="K14" s="55" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="54" t="str">
+    <row r="15" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="52" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H4,"000")</f>
         <v>101003002</v>
       </c>
-      <c r="B15" s="55" t="str">
+      <c r="B15" s="53" t="str">
         <f>규칙!B9</f>
         <v>Weapon</v>
       </c>
-      <c r="C15" s="55">
-        <v>0</v>
-      </c>
-      <c r="D15" s="55">
+      <c r="C15" s="53">
+        <v>0</v>
+      </c>
+      <c r="D15" s="53">
         <v>100</v>
       </c>
-      <c r="E15" s="55">
-        <v>0</v>
-      </c>
-      <c r="F15" s="55">
-        <v>0</v>
-      </c>
-      <c r="G15" s="55">
-        <v>0</v>
-      </c>
-      <c r="H15" s="56">
+      <c r="E15" s="53">
+        <v>0</v>
+      </c>
+      <c r="F15" s="53">
+        <v>0</v>
+      </c>
+      <c r="G15" s="53">
+        <v>0</v>
+      </c>
+      <c r="H15" s="54">
         <v>15000</v>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="53">
         <v>3</v>
       </c>
-      <c r="J15" s="55" t="str">
+      <c r="J15" s="53" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K15" s="57" t="s">
+      <c r="K15" s="55" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="54" t="str">
+    <row r="16" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="52" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H5,"000")</f>
         <v>101003003</v>
       </c>
-      <c r="B16" s="55" t="str">
+      <c r="B16" s="53" t="str">
         <f>규칙!B10</f>
         <v>Shield</v>
       </c>
-      <c r="C16" s="55">
-        <v>0</v>
-      </c>
-      <c r="D16" s="55">
-        <v>0</v>
-      </c>
-      <c r="E16" s="55">
+      <c r="C16" s="53">
+        <v>0</v>
+      </c>
+      <c r="D16" s="53">
+        <v>0</v>
+      </c>
+      <c r="E16" s="53">
         <v>45</v>
       </c>
-      <c r="F16" s="55">
-        <v>0</v>
-      </c>
-      <c r="G16" s="55">
-        <v>0</v>
-      </c>
-      <c r="H16" s="56">
+      <c r="F16" s="53">
+        <v>0</v>
+      </c>
+      <c r="G16" s="53">
+        <v>0</v>
+      </c>
+      <c r="H16" s="54">
         <v>12000</v>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="53">
         <v>3</v>
       </c>
-      <c r="J16" s="55" t="str">
+      <c r="J16" s="53" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K16" s="57" t="s">
+      <c r="K16" s="55" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="54" t="str">
+    <row r="17" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="52" t="str">
         <f>TEXT(규칙!$B$3,"000")&amp;TEXT(규칙!$E$6,"000")&amp;TEXT(규칙!H6,"000")</f>
         <v>101003004</v>
       </c>
-      <c r="B17" s="55" t="str">
+      <c r="B17" s="53" t="str">
         <f>규칙!B11</f>
         <v>Ring</v>
       </c>
-      <c r="C17" s="55">
-        <v>0</v>
-      </c>
-      <c r="D17" s="55">
-        <v>0</v>
-      </c>
-      <c r="E17" s="55">
-        <v>0</v>
-      </c>
-      <c r="F17" s="55">
+      <c r="C17" s="53">
+        <v>0</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0</v>
+      </c>
+      <c r="E17" s="53">
+        <v>0</v>
+      </c>
+      <c r="F17" s="53">
         <v>80</v>
       </c>
-      <c r="G17" s="55">
-        <v>0</v>
-      </c>
-      <c r="H17" s="56">
+      <c r="G17" s="53">
+        <v>0</v>
+      </c>
+      <c r="H17" s="54">
         <v>18000</v>
       </c>
-      <c r="I17" s="55">
+      <c r="I17" s="53">
         <v>3</v>
       </c>
-      <c r="J17" s="55" t="str">
+      <c r="J17" s="53" t="str">
         <f>규칙!$B$15</f>
         <v>Stone</v>
       </c>
-      <c r="K17" s="57" t="s">
+      <c r="K17" s="55" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1806,57 +2020,464 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF0A81C-159E-4364-9F32-5B6CE67F4D04}">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="16.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="61.296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" style="62" customWidth="1"/>
+    <col min="4" max="11" width="16.69921875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"001"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201001001</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"002"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201002001</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"003"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201003001</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="62">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"004"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201004001</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="62">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"005"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201005001</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="62">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"006"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201006001</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="62">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"007"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201007001</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="62">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"008"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201008001</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"009"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201009001</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"010"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201010001</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="62">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"011"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201011001</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="62">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"012"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201012001</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="62">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"013"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201013001</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="62">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"014"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201014001</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="62">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"015"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201015001</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"016"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201016001</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"017"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201017001</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="62">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"018"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201018001</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="62">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"019"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201019001</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="62">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"020"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201020001</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="62">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"021"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201021001</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="62">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"022"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201022001</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"023"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201023001</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"024"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201024001</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="62">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"025"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201025001</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="62">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"026"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201026001</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="62">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"027"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201027001</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="62">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"028"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201028001</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="62">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"029"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201029001</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"030"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201030001</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="62">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="str">
+        <f>TEXT(규칙!$B$4,"000")&amp;"031"&amp;TEXT(규칙!$H$9,"000")</f>
+        <v>201031001</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="62">
+        <v>15000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516DA3B0-E7F8-481C-A749-71C25F38EA06}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20.296875" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.69921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.296875" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.69921875" style="8" customWidth="1"/>
     <col min="6" max="6" width="12.69921875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.296875" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.69921875" style="8" customWidth="1"/>
     <col min="9" max="9" width="12.69921875" style="1" customWidth="1"/>
     <col min="11" max="11" width="8.796875" style="1"/>
     <col min="12" max="12" width="19.8984375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.796875" style="1"/>
-    <col min="14" max="14" width="14.09765625" style="16" customWidth="1"/>
+    <col min="13" max="13" width="16.69921875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.09765625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="59" t="s">
+    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="E2" s="59" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="60"/>
-      <c r="H2" s="59" t="s">
+      <c r="F2" s="70"/>
+      <c r="G2" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="60"/>
-      <c r="K2" s="61" t="s">
+      <c r="I2" s="70"/>
+      <c r="K2" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="15" t="str">
+      <c r="M2" s="13" t="str">
         <f>TEXT(B3, "000") &amp; TEXT(E3, "000") &amp; TEXT(H3, "000")</f>
         <v>101000001</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="2">
         <v>101</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="59" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="9">
@@ -1871,19 +2492,22 @@
       <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="61"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="14"/>
-      <c r="N3" s="17" t="str">
+      <c r="M3" s="15" t="str">
         <f>TEXT(B3, "000") &amp; TEXT(E3, "000") &amp; TEXT(H6, "000")</f>
         <v>101000004</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B4" s="2">
+        <v>201</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>61</v>
+      </c>
       <c r="E4" s="9">
         <v>1</v>
       </c>
@@ -1897,7 +2521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="E5" s="9">
@@ -1912,8 +2536,11 @@
       <c r="I5" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K5" s="74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="E6" s="10">
@@ -1928,94 +2555,178 @@
       <c r="I6" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
+      <c r="K6" s="74"/>
+    </row>
+    <row r="7" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="8" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="19" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9" s="20" t="s">
+      <c r="D8" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="73"/>
+      <c r="G8" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="73"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A9" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="24" t="s">
+      <c r="E10" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="68"/>
+      <c r="H10" s="9">
+        <v>2</v>
+      </c>
+      <c r="I10" s="57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="22" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E11" s="11">
+        <v>31</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="11">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A13" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14" s="20" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="22" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="16" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="63"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="19"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B18" s="21"/>
+      <c r="C18" s="57"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B19" s="21"/>
+      <c r="C19" s="57"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B20" s="21"/>
+      <c r="C20" s="57"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B21" s="21"/>
+      <c r="C21" s="57"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B22" s="21"/>
+      <c r="C22" s="66"/>
+    </row>
+    <row r="23" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="22"/>
+      <c r="C23" s="65"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="K5:K6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/08.Excel/GameData.xlsx
+++ b/Assets/08.Excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\My idle game\my-idle-game\Assets\08.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD51D7F-8F1C-46F7-823C-E6154FCE29D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B1B321-3C3D-42B3-90C4-7AAAF4753ABD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" activeTab="2" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="104">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -999,18 +999,9 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1033,6 +1024,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2444,25 +2444,25 @@
       <c r="A2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="70"/>
+      <c r="C2" s="67"/>
       <c r="D2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="70"/>
+      <c r="F2" s="67"/>
       <c r="G2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="H2" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="70"/>
-      <c r="K2" s="71" t="s">
+      <c r="I2" s="67"/>
+      <c r="K2" s="68" t="s">
         <v>44</v>
       </c>
       <c r="L2" s="12" t="s">
@@ -2492,7 +2492,7 @@
       <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="71"/>
+      <c r="K3" s="68"/>
       <c r="L3" s="12" t="s">
         <v>24</v>
       </c>
@@ -2536,7 +2536,7 @@
       <c r="I5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="74" t="s">
+      <c r="K5" s="71" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       <c r="I6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="74"/>
+      <c r="K6" s="71"/>
     </row>
     <row r="7" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="8" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -2571,17 +2571,17 @@
       <c r="D8" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="73"/>
-      <c r="G8" s="64" t="s">
+      <c r="F8" s="70"/>
+      <c r="G8" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="72" t="s">
+      <c r="H8" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="73"/>
+      <c r="I8" s="70"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="18" t="s">
@@ -2616,10 +2616,10 @@
       <c r="C10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="68"/>
+      <c r="F10" s="65"/>
       <c r="H10" s="9">
         <v>2</v>
       </c>
@@ -2684,35 +2684,34 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="63"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="19"/>
+      <c r="A17" s="74"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B18" s="21"/>
-      <c r="C18" s="57"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B19" s="21"/>
-      <c r="C19" s="57"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B20" s="21"/>
-      <c r="C20" s="57"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B21" s="21"/>
-      <c r="C21" s="57"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B22" s="21"/>
-      <c r="C22" s="66"/>
-    </row>
-    <row r="23" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="22"/>
-      <c r="C23" s="65"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="72"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B23" s="6"/>
+      <c r="C23" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/Assets/08.Excel/GameData.xlsx
+++ b/Assets/08.Excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\My idle game\my-idle-game\Assets\08.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B1B321-3C3D-42B3-90C4-7AAAF4753ABD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCC0C5A-6F50-4387-808C-E98F58D57D1F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" activeTab="2" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" activeTab="1" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemSheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -312,96 +312,7 @@
   </si>
   <si>
     <t>Assets/00.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/01.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/02.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/03.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/04.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/05.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/06.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/07.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/08.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/09.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/10.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/11.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/12.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/13.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/14.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/15.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/16.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/17.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/18.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/19.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/20.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/21.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/22.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/23.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/24.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/25.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/26.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/27.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/28.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/29.Externals/Myaddressable/G_coin.png[G_coin]</t>
-  </si>
-  <si>
-    <t>Assets/30.Externals/Myaddressable/G_coin.png[G_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -809,7 +720,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1002,6 +913,18 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1024,15 +947,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2058,8 +1972,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"002"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201002001</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>74</v>
+      <c r="B3" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C3" s="62">
         <v>10000</v>
@@ -2070,8 +1984,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"003"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201003001</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>75</v>
+      <c r="B4" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C4" s="62">
         <v>15000</v>
@@ -2082,8 +1996,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"004"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201004001</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>76</v>
+      <c r="B5" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C5" s="62">
         <v>20000</v>
@@ -2094,8 +2008,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"005"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201005001</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>77</v>
+      <c r="B6" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C6" s="62">
         <v>5000</v>
@@ -2106,8 +2020,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"006"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201006001</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>78</v>
+      <c r="B7" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C7" s="62">
         <v>8000</v>
@@ -2118,8 +2032,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"007"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201007001</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>79</v>
+      <c r="B8" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C8" s="62">
         <v>9000</v>
@@ -2130,8 +2044,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"008"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201008001</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>80</v>
+      <c r="B9" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C9" s="62">
         <v>10000</v>
@@ -2142,8 +2056,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"009"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201009001</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>81</v>
+      <c r="B10" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C10" s="62">
         <v>10000</v>
@@ -2154,8 +2068,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"010"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201010001</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>82</v>
+      <c r="B11" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C11" s="62">
         <v>15000</v>
@@ -2166,8 +2080,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"011"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201011001</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>83</v>
+      <c r="B12" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C12" s="62">
         <v>20000</v>
@@ -2178,8 +2092,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"012"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201012001</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>84</v>
+      <c r="B13" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C13" s="62">
         <v>5000</v>
@@ -2190,8 +2104,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"013"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201013001</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>85</v>
+      <c r="B14" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C14" s="62">
         <v>8000</v>
@@ -2202,8 +2116,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"014"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201014001</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>86</v>
+      <c r="B15" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="62">
         <v>9000</v>
@@ -2214,8 +2128,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"015"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201015001</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>87</v>
+      <c r="B16" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C16" s="62">
         <v>10000</v>
@@ -2226,8 +2140,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"016"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201016001</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>88</v>
+      <c r="B17" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C17" s="62">
         <v>10000</v>
@@ -2238,8 +2152,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"017"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201017001</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>89</v>
+      <c r="B18" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C18" s="62">
         <v>15000</v>
@@ -2250,8 +2164,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"018"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201018001</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>90</v>
+      <c r="B19" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C19" s="62">
         <v>20000</v>
@@ -2262,8 +2176,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"019"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201019001</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>91</v>
+      <c r="B20" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C20" s="62">
         <v>5000</v>
@@ -2274,8 +2188,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"020"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201020001</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>92</v>
+      <c r="B21" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C21" s="62">
         <v>8000</v>
@@ -2286,8 +2200,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"021"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201021001</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>93</v>
+      <c r="B22" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C22" s="62">
         <v>9000</v>
@@ -2298,8 +2212,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"022"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201022001</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>94</v>
+      <c r="B23" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C23" s="62">
         <v>10000</v>
@@ -2310,8 +2224,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"023"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201023001</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>95</v>
+      <c r="B24" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C24" s="62">
         <v>10000</v>
@@ -2322,8 +2236,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"024"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201024001</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>96</v>
+      <c r="B25" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C25" s="62">
         <v>15000</v>
@@ -2334,8 +2248,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"025"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201025001</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>97</v>
+      <c r="B26" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C26" s="62">
         <v>20000</v>
@@ -2346,8 +2260,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"026"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201026001</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>98</v>
+      <c r="B27" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C27" s="62">
         <v>5000</v>
@@ -2358,8 +2272,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"027"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201027001</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>99</v>
+      <c r="B28" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C28" s="62">
         <v>8000</v>
@@ -2370,8 +2284,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"028"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201028001</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>100</v>
+      <c r="B29" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C29" s="62">
         <v>9000</v>
@@ -2382,8 +2296,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"029"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201029001</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>101</v>
+      <c r="B30" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C30" s="62">
         <v>10000</v>
@@ -2394,8 +2308,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"030"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201030001</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>102</v>
+      <c r="B31" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C31" s="62">
         <v>10000</v>
@@ -2406,8 +2320,8 @@
         <f>TEXT(규칙!$B$4,"000")&amp;"031"&amp;TEXT(규칙!$H$9,"000")</f>
         <v>201031001</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>103</v>
+      <c r="B32" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C32" s="62">
         <v>15000</v>
@@ -2444,25 +2358,25 @@
       <c r="A2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="67"/>
+      <c r="C2" s="71"/>
       <c r="D2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="67"/>
+      <c r="F2" s="71"/>
       <c r="G2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="67"/>
-      <c r="K2" s="68" t="s">
+      <c r="I2" s="71"/>
+      <c r="K2" s="72" t="s">
         <v>44</v>
       </c>
       <c r="L2" s="12" t="s">
@@ -2492,7 +2406,7 @@
       <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="68"/>
+      <c r="K3" s="72"/>
       <c r="L3" s="12" t="s">
         <v>24</v>
       </c>
@@ -2536,7 +2450,7 @@
       <c r="I5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="71" t="s">
+      <c r="K5" s="75" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2555,7 +2469,7 @@
       <c r="I6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="71"/>
+      <c r="K6" s="75"/>
     </row>
     <row r="7" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="8" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -2571,17 +2485,17 @@
       <c r="D8" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="70"/>
+      <c r="F8" s="74"/>
       <c r="G8" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="70"/>
+      <c r="I8" s="74"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="18" t="s">
@@ -2616,10 +2530,10 @@
       <c r="C10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="64" t="s">
+      <c r="E10" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="65"/>
+      <c r="F10" s="69"/>
       <c r="H10" s="9">
         <v>2</v>
       </c>
@@ -2685,7 +2599,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="74"/>
+      <c r="A17" s="67"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
     </row>
@@ -2707,11 +2621,11 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B22" s="6"/>
-      <c r="C22" s="72"/>
+      <c r="C22" s="65"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B23" s="6"/>
-      <c r="C23" s="73"/>
+      <c r="C23" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="8">
